--- a/prenatal/VITAFOODS_EUROPE_2026_TARGET_LIST.xlsx
+++ b/prenatal/VITAFOODS_EUROPE_2026_TARGET_LIST.xlsx
@@ -502,14 +502,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -609,7 +609,7 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -649,7 +649,7 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -689,7 +689,7 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -729,7 +729,7 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -769,7 +769,7 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -809,7 +809,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -849,7 +849,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -889,7 +889,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -929,7 +929,7 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -969,7 +969,7 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -1009,7 +1009,7 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -1049,7 +1049,7 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -1089,7 +1089,7 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -1129,7 +1129,7 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>🔴 Must</t>
@@ -1169,7 +1169,7 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1209,7 +1209,7 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1249,7 +1249,7 @@
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1289,7 +1289,7 @@
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1329,7 +1329,7 @@
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1369,7 +1369,7 @@
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1409,7 +1409,7 @@
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1449,7 +1449,7 @@
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1489,7 +1489,7 @@
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1529,7 +1529,7 @@
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1569,7 +1569,7 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1609,7 +1609,7 @@
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1649,7 +1649,7 @@
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1689,7 +1689,7 @@
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>🟡 Strong</t>
@@ -1729,7 +1729,7 @@
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1769,7 +1769,7 @@
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1809,7 +1809,7 @@
       <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1849,7 +1849,7 @@
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1889,7 +1889,7 @@
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1929,7 +1929,7 @@
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -1969,7 +1969,7 @@
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2009,7 +2009,7 @@
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2049,7 +2049,7 @@
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2089,7 +2089,7 @@
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2129,7 +2129,7 @@
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2169,7 +2169,7 @@
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2209,7 +2209,7 @@
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>🟢 Visit</t>
@@ -2248,6 +2248,446 @@
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Lallemand Health Solutions</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Canada/France</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Probiotic / Prenatal Specialist</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Prenatis™ — clinically studied probiotic formula for maternal health + infant microbiome through breastfeeding. DIRECT prenatal/postnatal application</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Prenatis™ ingredient supply? India distribution? Evidence base + clinical study data? Pricing? Could be hero ingredient for Edit Postnatal SKU</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Jinkang Pharma</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Folate Specialist</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Magnafolate® L-methylfolate — pregnancy + infant-grade purity standard. Alternative to Quatrefolic</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Pricing comparison vs Quatrefolic? India distribution? Pregnancy/infant-grade certification docs? MOQ?</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Arjuna Natural</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Kerala-based — turmeric extracts, BCM-95 curcumin, ashwagandha. Perennial Vitafoods exhibitor</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>India-to-India supply chain? Women's health botanicals? KSM-66 alternatives?</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Akay (Synthite Industries)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Botanical extracts, oleoresins. Major Indian extract manufacturer</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Premium ingredient capability? Prenatal-grade specifications?</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Vidya Herbs</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Bangalore-based herbal extracts</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Women's health portfolio? Ashwagandha + shatavari sourcing?</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Natural Remedies</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Bangalore-based Ayurvedic/herbal extracts</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Women's health botanicals? Ayurvedic ingredients with modern clinical backing?</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Nutra Specialities</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Hyderabad-based botanical actives</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Premium ingredient offerings for prenatal? India supply chain?</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>🔴 Must</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Olive Lifesciences</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Bangalore-based natural ingredients</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Women's health portfolio? Quality certifications?</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>🟢 Visit</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Indian Spices Board / Pharmexcil collective stand</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Industry Network</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Government-organised India cluster. Useful for networking with peer Indian founders</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Other Indian DTC supplement founders attending? India regulatory updates? Government export support programs?</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>🟢 Visit</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Sami-Sabinsa Group (parent)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Indian Botanical Parent</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Parent company of Sabinsa — may have separate booth</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Larger portfolio than Sabinsa booth alone?</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>🟢 Visit</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Plant Lipids</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>India Pavilion</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Indian Botanical</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Natural extracts. Often co-located with India cluster</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Botanical specifications for women's health applications</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2266,7 +2706,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2297,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="110" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Day 1</t>
@@ -2310,21 +2750,21 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Branded ingredient suppliers (the formulation core)</t>
+          <t>Branded ingredient suppliers + India Pavilion walk</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>All 🔴 Must Meets — Balchem, dsm-firmenich, Gnosis (Quatrefolic), Ixoreal (KSM-66), Sabinsa, AB-Biotics, OmniActive, Lonza, Pharmalinea, Concordix, Gelita, Glanbia, BENEO, Aker BioMarine</t>
+          <t>All Must Meets — Balchem, dsm-firmenich, Gnosis (Quatrefolic), Ixoreal (KSM-66), Sabinsa, AB-Biotics, OmniActive, Lonza, Pharmalinea, Concordix, Gelita, Glanbia, BENEO, Aker BioMarine, Lallemand (Prenatis), Jinkang (Magnafolate). Walk India Pavilion: Arjuna Natural, Akay, Vidya Herbs, Natural Remedies, Nutra Specialities, Olive Lifesciences</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Arrive 9am sharp. Lowest crowds first 2 hours. Pre-book the top 5 if possible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1">
+          <t>Arrive 9am sharp. Lowest crowds first 2 hours. Pre-book top 5. India Pavilion walk in afternoon — collect every Indian booth's card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Day 2</t>
@@ -2351,7 +2791,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="110" customHeight="1">
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Day 3</t>
@@ -2369,7 +2809,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Berlin Packaging, TricorBraun, Selig, Adelphi, Eurofins, NSF, SGS, Clean Label Project, EAS Strategies, CPL, Synergy Flavours, India Pavilion, dsm-firmenich Innovation Wall</t>
+          <t>Berlin Packaging, TricorBraun, Selig, Adelphi, Eurofins, NSF, SGS, Clean Label Project, EAS Strategies, CPL, Synergy Flavours, dsm-firmenich Innovation Wall</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -2389,7 +2829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2474,7 +2914,7 @@
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Pre-book meetings via Vitafoods concierge (Balchem, dsm-firmenich, Gnosis, Ixoreal, Sabinsa)</t>
+          <t>Pre-book meetings via Vitafoods concierge (Balchem, dsm-firmenich, Gnosis, Ixoreal, Sabinsa, Lallemand, Jinkang)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2566,7 +3006,7 @@
       <c r="A11" s="9" t="inlineStr"/>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Set up Notion mobile / scanner app for real-time card capture</t>
+          <t>Find India Pavilion location at info desk on Day 1</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2574,13 +3014,17 @@
           <t>Aishu</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Cluster zone with Pharmexcil + Indian companies</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Bring portable charger (12+ hour days)</t>
+          <t>Set up Notion mobile / scanner app for real-time card capture</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -2594,7 +3038,7 @@
       <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Prepare 30-second pitch (use the manifesto)</t>
+          <t>Bring portable charger (12+ hour days)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -2602,25 +3046,39 @@
           <t>Aishu</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>'I'm building India's answer to a wellness market that hasn't kept up with how modern Indian couples actually live.'</t>
-        </is>
-      </c>
+      <c r="D13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" s="9" t="inlineStr">
         <is>
+          <t>Prepare 30-second pitch (use the manifesto)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Aishu</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>'I'm building India's answer to a wellness market that hasn't kept up with how modern Indian couples actually live.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
           <t>Save target list (this file) offline on phone for venue use</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Aishu</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>WiFi at trade shows is unreliable</t>
         </is>
@@ -2665,12 +3123,12 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>🔴 Must</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Branded ingredient suppliers whose products are in The Edit's spec. If you only meet 15 booths, meet these.</t>
+          <t>Branded ingredient suppliers whose products are in The Edit's spec, prenatal/women's health specialists, Indian Pavilion key booths. Top priority.</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -2682,7 +3140,7 @@
     <row r="3" ht="50" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>🟡 Strong</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -2699,7 +3157,7 @@
     <row r="4" ht="50" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>🟢 Visit</t>
+          <t>Visit</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
